--- a/artfynd/A 3914-2023 artfynd.xlsx
+++ b/artfynd/A 3914-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3914-2023 artfynd.xlsx
+++ b/artfynd/A 3914-2023 artfynd.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">

--- a/artfynd/A 3914-2023 artfynd.xlsx
+++ b/artfynd/A 3914-2023 artfynd.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">

--- a/artfynd/A 3914-2023 artfynd.xlsx
+++ b/artfynd/A 3914-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,6 +794,125 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131761963</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58441</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Egypten, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>685186</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6597928</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Henrik Spovin</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Henrik Spovin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3914-2023 artfynd.xlsx
+++ b/artfynd/A 3914-2023 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>131761963</v>
       </c>
       <c r="B3" t="n">
-        <v>58441</v>
+        <v>58444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3914-2023 artfynd.xlsx
+++ b/artfynd/A 3914-2023 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>131761963</v>
       </c>
       <c r="B3" t="n">
-        <v>58490</v>
+        <v>58492</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3914-2023 artfynd.xlsx
+++ b/artfynd/A 3914-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87922110</v>
+        <v>87921632</v>
       </c>
       <c r="B2" t="n">
-        <v>56522</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205976</v>
+        <v>102977</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,27 +703,28 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Åkers Runö, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685240.7786700253</v>
+        <v>685145</v>
       </c>
       <c r="R2" t="n">
-        <v>6597900.830090588</v>
+        <v>6598027</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -755,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-06-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-06-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +776,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Björn Averhed</t>
+          <t>Magnus Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -800,11 +786,11 @@
         <v>131761963</v>
       </c>
       <c r="B3" t="n">
-        <v>58492</v>
+        <v>58519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -913,6 +899,555 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>87921594</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Åkers Runö, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>685088</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6597986</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Nilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>87921595</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Åkers Runö, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>685013</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6598073</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Nilsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>87922034</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Åkers Runö, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>685003</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6597926</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-05-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-05-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Björn Averhed</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>87922047</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Åkers Runö, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>685267</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6597880</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-04-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-04-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Björn Averhed</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>87922110</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Åkers Runö, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>685241</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6597901</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-06-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-06-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Björn Averhed</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3914-2023 artfynd.xlsx
+++ b/artfynd/A 3914-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87921632</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131761963</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87921594</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87921595</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1228,6 +1253,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87922034</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1341,6 +1371,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87922047</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1448,8 +1483,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87922110</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>